--- a/extenbooks/S207_extenbook.xlsx
+++ b/extenbooks/S207_extenbook.xlsx
@@ -9482,7 +9482,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -10505,11 +10505,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10532,64 +10532,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US Mfg Productivity (BEA LTEG A173 + BLS FLS spliced 1950)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S207_research.json", "adequacy_report": "Technical/docs/chapters/CH2_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S207_DPR.md", "epr": "Technical/docs/series/S207_EPR.md", "loader": "Technical/code/L01_loaders/L01_S207_load.py", "processor": "Technical/code/P02_processors/P02_S207_construct.py", "validator": "Technical/code/V03_validators/V03_S207_validate.py", "processed": "Technical/data/processed/S207.parquet", "chopped_csv": "Technical/chopped/S207.csv", "extenbook_xlsx": "Technical/extenbooks/S207_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S207_extenbook.xlsx
+++ b/extenbooks/S207_extenbook.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E420"/>
+  <dimension ref="A1:E419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
@@ -2797,7 +2797,7 @@
         <v>3008.701225296663</v>
       </c>
       <c r="E125" t="n">
-        <v>827.6904361537961</v>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -3049,10 +3049,10 @@
         <v/>
       </c>
       <c r="D140" t="n">
-        <v>2937.84563127454</v>
+        <v>2937.254182242636</v>
       </c>
       <c r="E140" t="n">
-        <v>854.9351519190118</v>
+        <v>854.2720796622491</v>
       </c>
     </row>
     <row r="141"/>
@@ -9031,7 +9031,7 @@
         <v>2025</v>
       </c>
       <c r="B404" t="n">
-        <v>2937.84563127454</v>
+        <v>2937.254182242636</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B405" t="n">
-        <v>827.6904361537961</v>
+        <v>817.7443523023541</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B406" t="n">
-        <v>817.7443523023541</v>
+        <v>814.3114845426581</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B407" t="n">
-        <v>814.3114845426581</v>
+        <v>806.5812370935627</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -9120,10 +9120,10 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B408" t="n">
-        <v>806.5812370935627</v>
+        <v>814.3030912229523</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -9143,10 +9143,10 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B409" t="n">
-        <v>814.3030912229523</v>
+        <v>835.2947838073037</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -9166,10 +9166,10 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B410" t="n">
-        <v>835.2947838073037</v>
+        <v>830.477018296141</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -9189,10 +9189,10 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B411" t="n">
-        <v>830.477018296141</v>
+        <v>839.3655438646449</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
@@ -9212,10 +9212,10 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B412" t="n">
-        <v>839.3655438646449</v>
+        <v>839.1221375931749</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -9235,10 +9235,10 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B413" t="n">
-        <v>839.1221375931749</v>
+        <v>844.6113686808063</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -9258,10 +9258,10 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B414" t="n">
-        <v>844.6113686808063</v>
+        <v>888.4748574636213</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -9281,10 +9281,10 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B415" t="n">
-        <v>888.4748574636213</v>
+        <v>866.8200926225071</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -9304,10 +9304,10 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B416" t="n">
-        <v>866.8200926225071</v>
+        <v>822.9398172002803</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -9327,10 +9327,10 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B417" t="n">
-        <v>822.9398172002803</v>
+        <v>824.0897019999829</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B418" t="n">
-        <v>824.0897019999829</v>
+        <v>841.0358144861107</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -9373,10 +9373,10 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B419" t="n">
-        <v>841.0358144861107</v>
+        <v>854.2720796622491</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -9389,29 +9389,6 @@
         </is>
       </c>
       <c r="E419" t="inlineStr">
-        <is>
-          <t>index_1889=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B420" t="n">
-        <v>854.9351519190118</v>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>S207-D</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>FRED_COMPRMS</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
         <is>
           <t>index_1889=100</t>
         </is>
@@ -9571,7 +9548,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>In Shaikh (2016) the series appears as **Figure 2.7** in Chapter 2 ("The Wealth of Nations: A Long View").</t>
+          <t>In Shaikh (2016) the series appears as **Figure 2.5** in Chapter 2 ("Turbulent Trends and Hidden Structures").</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9768,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.7</t>
+          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.5</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10467,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T23:18:45.029196+00:00</t>
+          <t>2026-07-02T13:27:54.027216+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S207_extenbook.xlsx
+++ b/extenbooks/S207_extenbook.xlsx
@@ -10467,7 +10467,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T13:27:54.027216+00:00</t>
+          <t>2026-07-11T03:44:24.290232+00:00</t>
         </is>
       </c>
     </row>
@@ -10482,11 +10482,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10509,6 +10509,126 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Fig.2.5; book_period_validated; real data present. Units corrected: registry mixed_units string split - all four subseries are index (1889=100).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VREF 2026-07-02: extension subseries S207-C (FRED OPHMFG) and S207-D (FRED COMPRMS) refreshed to the LATEST FRED/ALFRED vintage (realtime pin 2026-05-18 -&gt; 2026-07-02) per USER RULING. Book rows (S207-A/B, 1889-2010) byte-identical; only 2025 changed: S207-C 2937.845631 -&gt; 2937.254182 (-0.591, -0.020%); S207-D 854.935152 -&gt; 854.272080 (-0.663, -0.078%). V03 PASS. See config/VINTAGE_MANIFEST.json + remediation_campaign/evidence_VREF.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>index (1889=100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
